--- a/data/trans_orig/IP2903-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2903-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>22667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>35341</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19228</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>26288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27747</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43537</t>
+          <t>42718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>16739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>24958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>33855</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49856</t>
+          <t>50555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50510</t>
+          <t>50224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>30562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70793</t>
+          <t>69350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92713</t>
+          <t>91342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25114</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21650</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35710</t>
+          <t>36123</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37862</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>56676</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32383</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49521</t>
+          <t>48924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31384</t>
+          <t>32122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47623</t>
+          <t>47841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68859</t>
+          <t>70494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93052</t>
+          <t>92303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>36744</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>30375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30929</t>
+          <t>31668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43668</t>
+          <t>44609</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36098</t>
+          <t>35627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>47958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70390</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88875</t>
+          <t>89452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21910</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30400</t>
+          <t>29681</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>46134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29612</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>16185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28456</t>
+          <t>29222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>54767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40632</t>
+          <t>40374</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41017</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57598</t>
+          <t>58417</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25665</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31497</t>
+          <t>31364</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45869</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>25627</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17514</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>19953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>34067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29127</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30733</t>
+          <t>30761</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>41789</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>25859</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37319</t>
+          <t>37834</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59726</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76134</t>
+          <t>76386</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38786</t>
+          <t>38477</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>27106</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>43959</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53803</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76568</t>
+          <t>77585</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10984</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>23371</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27843</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28113</t>
+          <t>27958</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46655</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68821</t>
+          <t>69848</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>86966</t>
+          <t>87098</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>62048</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>80109</t>
+          <t>80277</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>136361</t>
+          <t>136416</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>162507</t>
+          <t>161550</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,17%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62220</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>80805</t>
+          <t>80899</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>57813</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>77065</t>
+          <t>77943</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>125248</t>
+          <t>125531</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>152766</t>
+          <t>154514</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43957</t>
+          <t>44622</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>26194</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>43957</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>58161</t>
+          <t>60270</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>83126</t>
+          <t>82893</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>54216</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>46383</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>65230</t>
+          <t>65727</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>87948</t>
+          <t>86065</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>113366</t>
+          <t>112813</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>194118</t>
+          <t>192578</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>232729</t>
+          <t>231965</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>207014</t>
+          <t>205974</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>244556</t>
+          <t>246058</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>413238</t>
+          <t>412482</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>466694</t>
+          <t>467301</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>118186</t>
+          <t>118225</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>151356</t>
+          <t>150886</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>146354</t>
+          <t>149018</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>181472</t>
+          <t>183634</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>272867</t>
+          <t>273024</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>322976</t>
+          <t>323325</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>289042</t>
+          <t>288312</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>330723</t>
+          <t>328554</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>285120</t>
+          <t>285452</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>327311</t>
+          <t>326420</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>586863</t>
+          <t>585398</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>644251</t>
+          <t>646879</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46309</t>
+          <t>46161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22908</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>40382</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>23424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36543</t>
+          <t>36963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56157</t>
+          <t>56936</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74075</t>
+          <t>74069</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>40845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58802</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40069</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57647</t>
+          <t>56630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87058</t>
+          <t>86419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109749</t>
+          <t>110336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>13905</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>27153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>30429</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48035</t>
+          <t>48375</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>41745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>33209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49732</t>
+          <t>50133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63857</t>
+          <t>64419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86898</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30537</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>36049</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53732</t>
+          <t>54661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28111</t>
+          <t>27502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26670</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>42640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26503</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39756</t>
+          <t>39178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30238</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65778</t>
+          <t>65919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34380</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>19900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>34299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>63714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34500</t>
+          <t>34067</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>48278</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>36417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51563</t>
+          <t>51517</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75441</t>
+          <t>76246</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>96437</t>
+          <t>95362</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32353</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42754</t>
+          <t>42579</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>57466</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33976</t>
+          <t>33986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14750</t>
+          <t>14439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>24155</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>30423</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48162</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>31355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43239</t>
+          <t>43548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61250</t>
+          <t>61359</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53381</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26778</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44509</t>
+          <t>45488</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>67414</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>92299</t>
+          <t>92461</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33154</t>
+          <t>33120</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50190</t>
+          <t>50204</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53054</t>
+          <t>52953</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>75617</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60171</t>
+          <t>59109</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>79169</t>
+          <t>79398</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>56099</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>76671</t>
+          <t>75997</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>122350</t>
+          <t>123126</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>149900</t>
+          <t>150936</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>59614</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79193</t>
+          <t>80308</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>69607</t>
+          <t>70682</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>92147</t>
+          <t>90087</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>134227</t>
+          <t>136077</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>165392</t>
+          <t>164725</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>35460</t>
+          <t>35324</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>37556</t>
+          <t>38387</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>46036</t>
+          <t>47309</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>67344</t>
+          <t>68627</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>53719</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>73374</t>
+          <t>73739</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>46691</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>67920</t>
+          <t>66905</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>107481</t>
+          <t>105551</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>135792</t>
+          <t>133732</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>240259</t>
+          <t>239779</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>281544</t>
+          <t>280987</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>256083</t>
+          <t>255816</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>298709</t>
+          <t>299894</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>507907</t>
+          <t>506417</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>566039</t>
+          <t>568078</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>104329</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>137504</t>
+          <t>138761</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>136464</t>
+          <t>137938</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>173196</t>
+          <t>171904</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>251068</t>
+          <t>250916</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>298973</t>
+          <t>300625</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>297192</t>
+          <t>294882</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>338627</t>
+          <t>338753</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>280659</t>
+          <t>279708</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>324636</t>
+          <t>323832</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>586847</t>
+          <t>588357</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>648379</t>
+          <t>650487</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26925</t>
+          <t>26761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>48666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>37550</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>44454</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60759</t>
+          <t>60572</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78183</t>
+          <t>78360</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30427</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45965</t>
+          <t>46631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73339</t>
+          <t>72249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96154</t>
+          <t>96029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,48%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33036</t>
+          <t>33174</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>51425</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>31346</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>46969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>37353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>53872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72856</t>
+          <t>73416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96397</t>
+          <t>97106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>35950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>33154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46117</t>
+          <t>46227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49291</t>
+          <t>49402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72557</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92164</t>
+          <t>91115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26814</t>
+          <t>27684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19979</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34102</t>
+          <t>34575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57228</t>
+          <t>56375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39453</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>52701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38988</t>
+          <t>38999</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83353</t>
+          <t>82998</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104658</t>
+          <t>103047</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14235</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19678</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57521</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21251</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25752</t>
+          <t>26651</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>26584</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>31381</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48833</t>
+          <t>47532</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32774</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31649</t>
+          <t>32360</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43665</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>61145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,31%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>29279</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46960</t>
+          <t>46334</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40440</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58304</t>
+          <t>57841</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81327</t>
+          <t>80428</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41334</t>
+          <t>40301</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59422</t>
+          <t>59165</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63573</t>
+          <t>64735</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>91126</t>
+          <t>91038</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>117867</t>
+          <t>116506</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37283</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>56720</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45034</t>
+          <t>44524</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>87974</t>
+          <t>87281</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>114259</t>
+          <t>113298</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31435</t>
+          <t>31975</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>48973</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>40393</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59072</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>77713</t>
+          <t>77951</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>103218</t>
+          <t>102243</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>51079</t>
+          <t>51549</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>69849</t>
+          <t>70744</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>41276</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60448</t>
+          <t>59824</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>97381</t>
+          <t>97627</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>122769</t>
+          <t>123522</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>48696</t>
+          <t>48812</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>67574</t>
+          <t>68346</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>53299</t>
+          <t>54012</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>73396</t>
+          <t>74149</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>109082</t>
+          <t>108896</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>137259</t>
+          <t>137234</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>174185</t>
+          <t>175191</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>213377</t>
+          <t>213686</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>181207</t>
+          <t>180200</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>219387</t>
+          <t>220090</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>366362</t>
+          <t>367262</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>422108</t>
+          <t>422653</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>180502</t>
+          <t>179875</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>219455</t>
+          <t>218700</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>176142</t>
+          <t>180249</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>216724</t>
+          <t>218865</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>368828</t>
+          <t>366803</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>426157</t>
+          <t>425607</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>275301</t>
+          <t>273762</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>315692</t>
+          <t>317065</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>304196</t>
+          <t>303314</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>347574</t>
+          <t>346567</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>590268</t>
+          <t>589484</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>652471</t>
+          <t>650447</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
